--- a/SmartSearch/qna/MART_SmartSearch_QnA_Log_v1.1_20260817.xlsx
+++ b/SmartSearch/qna/MART_SmartSearch_QnA_Log_v1.1_20260817.xlsx
@@ -3357,7 +3357,7 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Resolved</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -3375,8 +3375,16 @@
           <t>19/08/2026</t>
         </is>
       </c>
-      <c r="K58" s="4" t="n"/>
-      <c r="L58" s="4" t="n"/>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>Đã chốt theo meeting BA 2026-08-24 (rule ưu tiên bổ sung #5): tiêu chí xếp hạng chính thức là SỐ TỪ KHOÁ TỪ QUERY MATCH được với sản phẩm (matching từ nhiều nhất → hiển thị lên đầu) — đây là tiêu chí XẾP HẠNG MỚI, đứng ngang/trên hệ thống tier hiện có, KHÔNG chỉ là tie-break cùng tier. Diễn giải này khớp với hướng của BRD FR-SP-01 (đếm số lần khớp trong tên sản phẩm), KHÔNG phải hướng "search volume" của Storyboard SS-SCR-002. Test case SS-SCR-002-SC1-TC3 (đang viết theo Storyboard) cần được rà soát lại. Xem test case mới SS-SCR-005-SC11-TC1 và INT-01-SC3-TC1.</t>
+        </is>
+      </c>
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -4010,7 +4018,7 @@
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>INT-01-SC1-TC1 (Out-of-stock override) vẫn có căn cứ BRD rõ ràng, không bị ảnh hưởng. INT-01-SC1-TC2 ('Business rule &gt; Relevance thuần') đang test 1 giả định thứ tự CHƯA CÓ CĂN CỨ — nếu thực tế là công thức blend 1 lần (không có tầng rời rạc), TC2 sai về bản chất và cần viết lại hoàn toàn.</t>
+          <t>INT-01-SC1-TC1 (Out-of-stock override) vẫn có căn cứ BRD rõ ràng, không bị ảnh hưởng. INT-01-SC1-TC2 ('Business rule &gt; Relevance thuần') đang test 1 giả định thứ tự CHƯA CÓ CĂN CỨ — nếu thực tế là công thức blend 1 lần (không có tầng rời rạc), TC2 sai về bản chất và cần viết lại hoàn toàn. [Cập nhật 24/08/2026: rule 5 (BA meeting) xác nhận "matching nhiều từ nhất" là 1 tiêu chí xếp hạng MỚI, đứng ngang/trên hệ thống tier — KHÔNG giải quyết trực tiếp câu hỏi về thứ tự 4 tầng ở trên, nhưng cần BA/TD xác nhận thêm vị trí tương đối của tiêu chí mới này trong chuỗi ưu tiên tổng thể. Xem INT-01-SC3-TC1.]</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
@@ -4064,7 +4072,7 @@
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>INT-01-SC2-TC1 chỉ có thể verify tính NHẤT QUÁN qua nhiều lần gọi (không random đảo lộn), không thể chấm Pass/Fail theo đúng thứ tự kỳ vọng vì chưa biết tiêu chí phụ chính thức là gì.</t>
+          <t>INT-01-SC2-TC1 chỉ có thể verify tính NHẤT QUÁN qua nhiều lần gọi (không random đảo lộn), không thể chấm Pass/Fail theo đúng thứ tự kỳ vọng vì chưa biết tiêu chí phụ chính thức là gì. [Cập nhật 24/08/2026: rule 5 xác nhận matchedWords (số từ khoá match) là 1 tiêu chí xếp hạng mới đã được BA chốt — có thể dùng làm 1 phần tiêu chí phụ cho trường hợp Scorecard bằng nhau, nhưng CHƯA đủ để đóng QnA này vì chưa rõ vị trí matchedWords so với các tiêu chí phụ khác (Product_ID, thời gian update, doanh số...). Xem INT-01-SC3-TC1.]</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
@@ -4134,6 +4142,60 @@
       <c r="K72" s="4" t="n"/>
       <c r="L72" s="4" t="n"/>
     </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>QnA-69</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Search Result / Zero-Result — field xác định "Active" cho rule lọc Elasticsearch (rule 2, BA meeting 2026-08-24) chưa được BA/Dev xác nhận chính thức</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>Meeting BA 2026-08-24 chốt rule: "hệ thống OpenSearch kết hợp cùng với Elastic Search để xem sản phẩm nào sẽ hiển thị ở Search result và autocomplete (Elastic Search giới hạn chỉ hiển thị các sản phẩm đang Active)" — nhưng KHÔNG nêu rõ field cụ thể nào định nghĩa "Active". Trong dữ liệu catalogue thật (ProductInfo) có ít nhất 4 field liên quan, cho ra 4 tập loại trừ khác nhau: `status` (Magento catalog status, 1=Enabled/2=Disabled — loại 208/16340 SKU), `ec_status` (0/1), `visibility_search` (bool — false ở 63 SKU), `visibility_catalog` (bool — false ở 2453 SKU). Hiện tại bộ test data/engine giả lập đang TẠM dùng `status` theo chỉ định của stakeholder trong lúc chờ xác nhận. Cần BA/Dev chốt: field chính thức (có thể là 1 field hoặc kết hợp nhiều field) định nghĩa "Active" cho mục đích hiển thị Search/Autocomplete.</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>BA meeting 24/08/2026, rule 2 (chưa có REQ ID chính thức) — liên quan SS-SCR-005-SC12-TC1, INT-09-SC5-TC1</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>QC (rà soát rule mới từ BA meeting 24/08/2026)</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>BA / Dev</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC12-TC1 và INT-09-SC5-TC1 đang test theo field tạm `status` — có thể SAI/cần rà soát lại nếu field chính thức hoá ra là ec_status/visibility_search/visibility_catalog hoặc kết hợp nhiều field.</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>SS-SCR-005-SC12-TC1, INT-09-SC5-TC1</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>24/08/2026</t>
+        </is>
+      </c>
+      <c r="K73" s="4" t="n"/>
+      <c r="L73" s="4" t="n"/>
+    </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
@@ -4141,7 +4203,7 @@
         </is>
       </c>
       <c r="B74" s="5">
-        <f>COUNTA(A5:A72)</f>
+        <f>COUNTA(A5:A73)</f>
         <v/>
       </c>
     </row>
